--- a/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
+++ b/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Human Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB79B57B-F75C-4797-BBEB-F8D398CBC95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BC334C-D2EB-4445-91CE-AD6CF94D151C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,6 +90,46 @@
   </si>
   <si>
     <t>delaytime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가득이요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50000원치요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋은 하루 보내세요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기름값이 올랐네요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급 휘발유 가득이요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경유 가득이요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휘발유 70000원치요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흠흠 안녕하세요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새들은 지저귀고 꽃들은 피어나고…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수고하세요!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -477,20 +517,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.6640625" style="1"/>
     <col min="3" max="3" width="9.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.4140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.9140625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="11.1640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.33203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.58203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.25" style="1" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="30.33203125" style="1" customWidth="1"/>
     <col min="14" max="14" width="11.25" style="1" customWidth="1"/>
     <col min="15" max="16384" width="8.6640625" style="1"/>
   </cols>
@@ -547,10 +588,40 @@
         <v>16</v>
       </c>
       <c r="C2" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.45">
@@ -565,6 +636,20 @@
       </c>
       <c r="D3" s="1">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
+++ b/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Human Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BC334C-D2EB-4445-91CE-AD6CF94D151C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9578F05-189E-40A5-981B-AAD7BB65D07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="89">
   <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -105,10 +105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기름값이 올랐네요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>고급 휘발유 가득이요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -121,15 +117,263 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>흠흠 안녕하세요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>새들은 지저귀고 꽃들은 피어나고…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수고하세요!</t>
+    <t>아저씨 저기요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아저씨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아저씨 창문내려봐요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창문 내리라고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내말이 말같지 않아?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내말이 우스워?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내가 만만해보이지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아저씨 창문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창문좀 내려봐요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이거 아까 그쪽이 떨어뜨리고 가길래</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>히히</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤헤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무도 날 막을수 없어!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주려고 왔지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어엉 수고하고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나 재정신이거든</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자판기가 왜이러지?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어어? 왜 안나와 이거</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역시 기계는 때려야</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정신을 차리지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래 안 그래?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이런 하..진짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기 사장 나오라 그래</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜 안나와 이거</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아 돈을 까먹고 못넣었네</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>깜빡했구만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴... 다행이네</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장 부르라고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐야?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이 XX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>니 뭔데 보자마자 욕질이야</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사람이 쳤으면 사과를 해야지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아 예예 죄송합니다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>때려? 지금 뭐 싸우자고?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하.. 사과하면 끝나?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>들어와</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사람 놀리나?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>힘이 하도 약해서 솜털이 치는줄 알았어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제대로 해야지?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밤새도록 토하게 해줄게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이어 네짝 전부 갈아줘요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이어좀 수리해 주세요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이어 교체좀 할께요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕하세요 가득이요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕하세요 타이어좀 봐주세요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기름값이 올랐네요 40000원치요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내려</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이어 너무 비싼거 아니에요? 가장 싼거로 해주세요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국타이어랑 금호랑 뭐가 나아요? 무난한거 주세요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이거 더 탈 수 있을 것 같은데... 마모선 보니까 갈 때 됐네요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나와</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금 뭐하는거지?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운전 누가 가르쳤어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운전대 내가 다시는 못잡게 해줄께</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나랑 장난해?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니 무슨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너같은 알바 말고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기름값이 이게 말이 돼?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사랑했나봐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잊을수 없나봐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자꾸 생각나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>견딜수가 없어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후회하나봐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>널 기다리나봐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -517,19 +761,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.6640625" style="1"/>
     <col min="3" max="3" width="9.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.9140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.4140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="47" style="1" customWidth="1"/>
+    <col min="10" max="10" width="64.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="43.9140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="20.83203125" style="1" customWidth="1"/>
     <col min="13" max="13" width="30.33203125" style="1" customWidth="1"/>
     <col min="14" max="14" width="11.25" style="1" customWidth="1"/>
@@ -600,28 +844,22 @@
         <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.45">
@@ -632,10 +870,31 @@
         <v>15</v>
       </c>
       <c r="C3" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.45">
@@ -643,13 +902,310 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+      <c r="D11" s="1">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1">
+        <v>30</v>
+      </c>
+      <c r="D12" s="1">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>12</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
+++ b/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Human Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9578F05-189E-40A5-981B-AAD7BB65D07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1B3B79-2B75-4A5E-A5A9-75C2AAA3C062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
   <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -157,30 +157,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>히히</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>헤헤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아무도 날 막을수 없어!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>하하</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>주려고 왔지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>어엉 수고하고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>나 재정신이거든</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -265,14 +249,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>사람 놀리나?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>힘이 하도 약해서 솜털이 치는줄 알았어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>제대로 해야지?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -374,6 +350,106 @@
   </si>
   <si>
     <t>널 기다리나봐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reputeDown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어 수고하고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"자판기 이용하면 사장이 때리는 가게 가지마세요"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"주유하는 손님 때리는 주유소 망해라"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"손님끼리 대화도 못하게 하는 쓰레기 주유소"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"시비거는 손님이 있어도 관리 하나도 안하는 주유소 "</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"사람들이 싸우는데 무섭고 사장은 말리지도 않네요"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"정신병자가 날뛰는 역대급 주유소"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"무료로 UFC를 볼 수 있는 최악의 주유소"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"너무 시끄럽고 무서워요..관리도 안하는 주유소"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후우..후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>히얏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"가격좀 비싸다고 말하면 사람을 패버리는 미친 주유소"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"춤추기만 해도 사람 패는 너무 불친절한 주유소"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>히히히히힣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤헤헤헤헤헤헿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하하하하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공짜로는 못갈아주나요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저 돈이 없어서 공짜로 갈아주세요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공짜로 갈아 달라고요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공짜로 안달아주면 차 안뺼껍니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저 돈 못내요 빨리요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공짜로 갈아 주시는건가요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"진상의 정석이 있어도 진상 대응은 최악"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"진상 대처를 못해서 제 시간만 날린 주유소"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -761,26 +837,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.6640625" style="1"/>
     <col min="3" max="3" width="9.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="22.9140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="26.4140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="43.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="31.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="30.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="47" style="1" customWidth="1"/>
     <col min="10" max="10" width="64.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="43.9140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="49.5" style="1" customWidth="1"/>
     <col min="12" max="12" width="20.83203125" style="1" customWidth="1"/>
     <col min="13" max="13" width="30.33203125" style="1" customWidth="1"/>
     <col min="14" max="14" width="11.25" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.6640625" style="1"/>
+    <col min="15" max="15" width="56.1640625" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -823,8 +900,11 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -844,13 +924,13 @@
         <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>21</v>
@@ -861,8 +941,11 @@
       <c r="L2" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="O2" s="1" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -896,8 +979,11 @@
       <c r="K3" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="O3" s="1" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -920,13 +1006,16 @@
         <v>33</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>39</v>
+        <v>84</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -940,25 +1029,28 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,22 +1064,25 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,22 +1096,25 @@
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>40</v>
+      <c r="O7" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,25 +1128,28 @@
         <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>45</v>
+      <c r="O8" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -1062,22 +1163,25 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1091,25 +1195,28 @@
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>63</v>
+      <c r="O10" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,25 +1230,28 @@
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="I11" s="1" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -1155,28 +1265,31 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="J12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>73</v>
+      <c r="O12" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,22 +1303,60 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
+++ b/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Human Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoYK\Documents\GitHub\Engine GenP 3D\LastDance\Assets\Resources\DataBase\Human Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1B3B79-2B75-4A5E-A5A9-75C2AAA3C062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="16224"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -81,18 +80,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>inoder</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>random</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>delaytime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>가득이요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -450,13 +437,25 @@
   </si>
   <si>
     <t>"진상 대처를 못해서 제 시간만 날린 주유소"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>delayTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Random</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InOrder</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -836,28 +835,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" style="1"/>
-    <col min="3" max="3" width="9.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.9140625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="8.69921875" style="1"/>
+    <col min="3" max="3" width="9.296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.19921875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.8984375" style="1" customWidth="1"/>
     <col min="6" max="6" width="43.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="31.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="31.296875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.296875" style="1" customWidth="1"/>
     <col min="9" max="9" width="47" style="1" customWidth="1"/>
-    <col min="10" max="10" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="64.296875" style="1" customWidth="1"/>
     <col min="11" max="11" width="49.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="30.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.25" style="1" customWidth="1"/>
-    <col min="15" max="15" width="56.1640625" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.6640625" style="1"/>
+    <col min="12" max="12" width="20.796875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="30.296875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.19921875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="56.19921875" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.69921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -865,7 +864,7 @@
         <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -901,15 +900,15 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="C2" s="1">
         <v>30</v>
@@ -918,39 +917,39 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -959,36 +958,36 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="O3" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -997,30 +996,30 @@
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>87</v>
-      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -1029,33 +1028,33 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="O5" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
@@ -1064,30 +1063,30 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -1096,30 +1095,30 @@
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
@@ -1128,33 +1127,33 @@
         <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="O8" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
@@ -1163,30 +1162,30 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="O9" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -1195,33 +1194,33 @@
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="O10" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1230,33 +1229,33 @@
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="O11" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="C12" s="1">
         <v>30</v>
@@ -1265,36 +1264,36 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="J12" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C13" s="1">
         <v>5</v>
@@ -1303,33 +1302,33 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="O13" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="C14" s="1">
         <v>5</v>
@@ -1338,29 +1337,30 @@
         <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="O14" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
+++ b/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoYK\Documents\GitHub\Engine GenP 3D\LastDance\Assets\Resources\DataBase\Human Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Human Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F94663-F3E8-43ED-9264-3D8D3B0AC1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="16224"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -240,30 +241,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>밤새도록 토하게 해줄게</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>타이어 네짝 전부 갈아줘요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>타이어좀 수리해 주세요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>타이어 교체좀 할께요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>안녕하세요 가득이요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>안녕하세요 타이어좀 봐주세요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>기름값이 올랐네요 40000원치요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -272,18 +253,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>타이어 너무 비싼거 아니에요? 가장 싼거로 해주세요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한국타이어랑 금호랑 뭐가 나아요? 무난한거 주세요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이거 더 탈 수 있을 것 같은데... 마모선 보니까 갈 때 됐네요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>나와</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -388,10 +357,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"가격좀 비싸다고 말하면 사람을 패버리는 미친 주유소"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"춤추기만 해도 사람 패는 너무 불친절한 주유소"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -408,35 +373,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공짜로는 못갈아주나요?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저 돈이 없어서 공짜로 갈아주세요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공짜로 갈아 달라고요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공짜로 안달아주면 차 안뺼껍니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저 돈 못내요 빨리요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공짜로 갈아 주시는건가요?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"진상의 정석이 있어도 진상 대응은 최악"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"진상 대처를 못해서 제 시간만 날린 주유소"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -455,7 +392,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -835,28 +772,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O14"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="8.69921875" style="1"/>
-    <col min="3" max="3" width="9.296875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.19921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.8984375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" style="1"/>
+    <col min="3" max="3" width="9.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.9140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="43.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="31.296875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30.296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="47" style="1" customWidth="1"/>
-    <col min="10" max="10" width="64.296875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="64.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="49.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="20.796875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="30.296875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.19921875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="56.19921875" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.69921875" style="1"/>
+    <col min="12" max="12" width="20.83203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="30.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="56.1640625" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -864,7 +801,7 @@
         <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -900,15 +837,15 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C2" s="1">
         <v>30</v>
@@ -923,13 +860,13 @@
         <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>18</v>
@@ -941,15 +878,15 @@
         <v>20</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -979,15 +916,15 @@
         <v>27</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -1008,18 +945,18 @@
         <v>32</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -1028,33 +965,33 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
@@ -1063,13 +1000,13 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>40</v>
@@ -1078,15 +1015,15 @@
         <v>45</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -1095,30 +1032,30 @@
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>33</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
@@ -1145,15 +1082,15 @@
         <v>38</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
@@ -1177,15 +1114,15 @@
         <v>44</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -1206,21 +1143,21 @@
         <v>51</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>54</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1241,121 +1178,45 @@
         <v>53</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C12" s="1">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D12" s="1">
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="1">
-        <v>5</v>
-      </c>
-      <c r="D13" s="1">
-        <v>12</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="1">
-        <v>5</v>
-      </c>
-      <c r="D14" s="1">
-        <v>13</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
+++ b/Assets/Resources/DataBase/Human Data/HumanDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Human Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F94663-F3E8-43ED-9264-3D8D3B0AC1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E2EABED-6D0A-4283-BEF9-ABDC96CCF179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="91">
   <si>
     <t>type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -285,30 +286,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>사랑했나봐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>잊을수 없나봐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>자꾸 생각나</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>견딜수가 없어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>후회하나봐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>널 기다리나봐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>reputeDown</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -386,6 +363,26 @@
   </si>
   <si>
     <t>InOrder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간적인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사나이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뛰는놈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그위에 뛰는놈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간 여자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -801,7 +798,7 @@
         <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -837,7 +834,7 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.45">
@@ -845,7 +842,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1">
         <v>30</v>
@@ -878,7 +875,7 @@
         <v>20</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.45">
@@ -886,7 +883,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
@@ -916,7 +913,7 @@
         <v>27</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
@@ -924,7 +921,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
@@ -945,10 +942,10 @@
         <v>32</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
@@ -956,7 +953,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -983,7 +980,7 @@
         <v>61</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
@@ -991,7 +988,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
@@ -1015,7 +1012,7 @@
         <v>45</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.45">
@@ -1023,7 +1020,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -1032,22 +1029,22 @@
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>33</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.45">
@@ -1055,7 +1052,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
@@ -1082,7 +1079,7 @@
         <v>38</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.45">
@@ -1090,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C9" s="1">
         <v>5</v>
@@ -1114,7 +1111,7 @@
         <v>44</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
@@ -1122,7 +1119,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -1143,13 +1140,13 @@
         <v>51</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>54</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.45">
@@ -1157,7 +1154,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1178,10 +1175,10 @@
         <v>53</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
@@ -1189,7 +1186,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
@@ -1198,25 +1195,22 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
